--- a/code/resultados/NWJSSP_OADG_NEH(InsertionMixedImprovement).xlsx
+++ b/code/resultados/NWJSSP_OADG_NEH(InsertionMixedImprovement).xlsx
@@ -15,6 +15,7 @@
     <sheet name="ft20r" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="tai_j10_m10_1" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="tai_j10_m10_1r" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="tai_j100_m10_1" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +429,7 @@
         <v>308</v>
       </c>
       <c r="B1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2">
@@ -470,7 +471,7 @@
         <v>337</v>
       </c>
       <c r="B1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2">
@@ -512,7 +513,7 @@
         <v>10374</v>
       </c>
       <c r="B1" t="n">
-        <v>149</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2">
@@ -566,7 +567,7 @@
         <v>10785</v>
       </c>
       <c r="B1" t="n">
-        <v>138</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2">
@@ -620,7 +621,7 @@
         <v>17657</v>
       </c>
       <c r="B1" t="n">
-        <v>2271</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="2">
@@ -704,7 +705,7 @@
         <v>17999</v>
       </c>
       <c r="B1" t="n">
-        <v>1711</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="2">
@@ -788,7 +789,7 @@
         <v>100573</v>
       </c>
       <c r="B1" t="n">
-        <v>123</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2">
@@ -842,7 +843,7 @@
         <v>100573</v>
       </c>
       <c r="B1" t="n">
-        <v>180</v>
+        <v>152</v>
       </c>
       <c r="C1" t="inlineStr"/>
       <c r="D1" t="inlineStr"/>
@@ -888,4 +889,328 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:CV2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>6322542</v>
+      </c>
+      <c r="B1" t="n">
+        <v>7200130</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>57497</v>
+      </c>
+      <c r="B2" t="n">
+        <v>62049</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36016</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32411</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12596</v>
+      </c>
+      <c r="F2" t="n">
+        <v>12217</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38120</v>
+      </c>
+      <c r="H2" t="n">
+        <v>120606</v>
+      </c>
+      <c r="I2" t="n">
+        <v>121827</v>
+      </c>
+      <c r="J2" t="n">
+        <v>73474</v>
+      </c>
+      <c r="K2" t="n">
+        <v>17798</v>
+      </c>
+      <c r="L2" t="n">
+        <v>89798</v>
+      </c>
+      <c r="M2" t="n">
+        <v>90667</v>
+      </c>
+      <c r="N2" t="n">
+        <v>5971</v>
+      </c>
+      <c r="O2" t="n">
+        <v>53437</v>
+      </c>
+      <c r="P2" t="n">
+        <v>45539</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>94334</v>
+      </c>
+      <c r="R2" t="n">
+        <v>62345</v>
+      </c>
+      <c r="S2" t="n">
+        <v>56206</v>
+      </c>
+      <c r="T2" t="n">
+        <v>38140</v>
+      </c>
+      <c r="U2" t="n">
+        <v>107246</v>
+      </c>
+      <c r="V2" t="n">
+        <v>94724</v>
+      </c>
+      <c r="W2" t="n">
+        <v>5207</v>
+      </c>
+      <c r="X2" t="n">
+        <v>104692</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>111937</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>7618</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>45619</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>78299</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>31478</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>25459</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>9492</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>80516</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>66368</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>102236</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>21775</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>75414</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>933</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>60870</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>53479</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>81437</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>69126</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>52164</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>43926</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>86826</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>6699</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>88053</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>51046</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>113274</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>70439</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>26161</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>116428</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>127192</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>129914</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>18060</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>100746</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>50439</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>32634</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>60378</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>72029</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>125528</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>56060</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>2057</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>98568</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>44917</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>17230</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>76630</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>95758</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>49208</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>89086</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>83564</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>4476</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>114588</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>68290</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>21447</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>64189</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>49983</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>10264</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>41794</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>39073</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>98408</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>104492</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>105084</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>28363</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>58689</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>25333</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>28820</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>74410</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>14162</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>24439</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>110451</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>85680</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>19816</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>40042</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>79649</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>116541</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>35291</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>13934</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>